--- a/assets/libreoffice_calc_njc/7232142e-4f9c-4994-a12a-ab2d8feef1ea/QtrAnnual_L2_10.xlsx
+++ b/assets/libreoffice_calc_njc/7232142e-4f9c-4994-a12a-ab2d8feef1ea/QtrAnnual_L2_10.xlsx
@@ -151,12 +151,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -178,7 +182,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -216,188 +220,188 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="2" t="n">
         <v>150000</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="2" t="n">
         <v>120000</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="2" t="n">
         <v>165000</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="2" t="n">
         <v>125000</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="2" t="n">
         <v>180000</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="2" t="n">
         <v>130000</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="2" t="n">
         <v>200000</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="2" t="n">
         <v>140000</v>
       </c>
-      <c r="J2" s="0" t="n">
-        <f aca="false">SUM(B2:H2)</f>
-        <v>1070000</v>
-      </c>
-      <c r="K2" s="0" t="n">
-        <f aca="false">SUM(C2,E2,G2,I2)</f>
+      <c r="J2" s="2" t="n">
+        <f aca="false">SUM(B2,D2,F2,H2)</f>
+        <v>695000</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <f aca="false">C2+E2+G2+I2</f>
         <v>515000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="2" t="n">
         <v>80000</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="2" t="n">
         <v>60000</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="2" t="n">
         <v>90000</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="2" t="n">
         <v>65000</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="2" t="n">
         <v>95000</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="2" t="n">
         <v>70000</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="2" t="n">
         <v>110000</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="2" t="n">
         <v>75000</v>
       </c>
-      <c r="J3" s="0" t="n">
-        <f aca="false">SUM(B3:H3)</f>
-        <v>570000</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <f aca="false">SUM(C3:I3)</f>
-        <v>565000</v>
+      <c r="J3" s="2" t="n">
+        <f aca="false">SUM(B3,D3,F3,H3)</f>
+        <v>375000</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <f aca="false">C3+E3+G3+I3</f>
+        <v>270000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="2" t="n">
         <v>200000</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="2" t="n">
         <v>100000</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="2" t="n">
         <v>220000</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="2" t="n">
         <v>110000</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="2" t="n">
         <v>250000</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="2" t="n">
         <v>120000</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="2" t="n">
         <v>280000</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="2" t="n">
         <v>130000</v>
       </c>
-      <c r="J4" s="0" t="n">
-        <f aca="false">SUM(B4:H4)</f>
-        <v>1280000</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <f aca="false">SUM(C4:I4)</f>
-        <v>1210000</v>
+      <c r="J4" s="2" t="n">
+        <f aca="false">SUM(B4,D4,F4,H4)</f>
+        <v>950000</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <f aca="false">C4+E4+G4+I4</f>
+        <v>460000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="2" t="n">
         <v>25000</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="2" t="n">
         <v>32000</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="2" t="n">
         <v>26000</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="2" t="n">
         <v>35000</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="2" t="n">
         <v>28000</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="2" t="n">
         <v>38000</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="2" t="n">
         <v>30000</v>
       </c>
-      <c r="J5" s="0" t="n">
-        <f aca="false">SUM(B5:H5)</f>
-        <v>214000</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <f aca="false">SUM(C5:I5)</f>
-        <v>214000</v>
+      <c r="J5" s="2" t="n">
+        <f aca="false">SUM(B5,D5,F5,H5)</f>
+        <v>135000</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <f aca="false">C5+E5+G5+I5</f>
+        <v>109000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="2" t="n">
         <v>100000</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="2" t="n">
         <v>85000</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="2" t="n">
         <v>110000</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="2" t="n">
         <v>90000</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="2" t="n">
         <v>120000</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="2" t="n">
         <v>95000</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="2" t="n">
         <v>130000</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="2" t="n">
         <v>100000</v>
       </c>
-      <c r="J6" s="0" t="n">
-        <f aca="false">SUM(B6:H6)</f>
-        <v>730000</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <f aca="false">SUM(C6:I6)</f>
-        <v>730000</v>
+      <c r="J6" s="2" t="n">
+        <f aca="false">SUM(B6,D6,F6,H6)</f>
+        <v>460000</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <f aca="false">C6+E6+G6+I6</f>
+        <v>370000</v>
       </c>
     </row>
   </sheetData>

--- a/assets/libreoffice_calc_njc/7232142e-4f9c-4994-a12a-ab2d8feef1ea/QtrAnnual_L2_10.xlsx
+++ b/assets/libreoffice_calc_njc/7232142e-4f9c-4994-a12a-ab2d8feef1ea/QtrAnnual_L2_10.xlsx
@@ -77,7 +77,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -99,14 +99,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -151,12 +143,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -184,7 +172,7 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -220,186 +208,186 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>150000</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="1" t="n">
         <v>120000</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="1" t="n">
         <v>165000</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="1" t="n">
         <v>125000</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>180000</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="1" t="n">
         <v>130000</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="1" t="n">
         <v>200000</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="1" t="n">
         <v>140000</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="1" t="n">
         <f aca="false">SUM(B2,D2,F2,H2)</f>
         <v>695000</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <f aca="false">C2+E2+G2+I2</f>
         <v>515000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="1" t="n">
         <v>80000</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="1" t="n">
         <v>60000</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="1" t="n">
         <v>90000</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="1" t="n">
         <v>65000</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>95000</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="1" t="n">
         <v>70000</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="1" t="n">
         <v>110000</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="1" t="n">
         <v>75000</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="1" t="n">
         <f aca="false">SUM(B3,D3,F3,H3)</f>
         <v>375000</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <f aca="false">C3+E3+G3+I3</f>
         <v>270000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>200000</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="1" t="n">
         <v>220000</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="1" t="n">
         <v>110000</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>250000</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>120000</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="1" t="n">
         <v>280000</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="1" t="n">
         <v>130000</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="1" t="n">
         <f aca="false">SUM(B4,D4,F4,H4)</f>
         <v>950000</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <f aca="false">C4+E4+G4+I4</f>
         <v>460000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1" t="n">
         <v>30000</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="1" t="n">
         <v>25000</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="1" t="n">
         <v>32000</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="1" t="n">
         <v>26000</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>35000</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="1" t="n">
         <v>28000</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="1" t="n">
         <v>38000</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="1" t="n">
         <v>30000</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="1" t="n">
         <f aca="false">SUM(B5,D5,F5,H5)</f>
         <v>135000</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <f aca="false">C5+E5+G5+I5</f>
         <v>109000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="1" t="n">
         <v>85000</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="1" t="n">
         <v>110000</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="1" t="n">
         <v>90000</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>120000</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>95000</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="1" t="n">
         <v>130000</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="1" t="n">
         <f aca="false">SUM(B6,D6,F6,H6)</f>
         <v>460000</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <f aca="false">C6+E6+G6+I6</f>
         <v>370000</v>
       </c>

--- a/assets/libreoffice_calc_njc/7232142e-4f9c-4994-a12a-ab2d8feef1ea/QtrAnnual_L2_10.xlsx
+++ b/assets/libreoffice_calc_njc/7232142e-4f9c-4994-a12a-ab2d8feef1ea/QtrAnnual_L2_10.xlsx
@@ -277,7 +277,7 @@
         <v>375000</v>
       </c>
       <c r="K3" s="1" t="n">
-        <f aca="false">C3+E3+G3+I3</f>
+        <f aca="false">SUM(C3,E3,G3,I3)</f>
         <v>270000</v>
       </c>
     </row>
@@ -314,7 +314,7 @@
         <v>950000</v>
       </c>
       <c r="K4" s="1" t="n">
-        <f aca="false">C4+E4+G4+I4</f>
+        <f aca="false">SUM(C4,E4,G4,I4)</f>
         <v>460000</v>
       </c>
     </row>
@@ -351,7 +351,7 @@
         <v>135000</v>
       </c>
       <c r="K5" s="1" t="n">
-        <f aca="false">C5+E5+G5+I5</f>
+        <f aca="false">SUM(C5,E5,G5,I5)</f>
         <v>109000</v>
       </c>
     </row>
@@ -388,7 +388,7 @@
         <v>460000</v>
       </c>
       <c r="K6" s="1" t="n">
-        <f aca="false">C6+E6+G6+I6</f>
+        <f aca="false">SUM(C6,E6,G6,I6)</f>
         <v>370000</v>
       </c>
     </row>

--- a/assets/libreoffice_calc_njc/7232142e-4f9c-4994-a12a-ab2d8feef1ea/QtrAnnual_L2_10.xlsx
+++ b/assets/libreoffice_calc_njc/7232142e-4f9c-4994-a12a-ab2d8feef1ea/QtrAnnual_L2_10.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Q4 Cost</t>
   </si>
   <si>
-    <t xml:space="preserve">Annual Revenue</t>
+    <t xml:space="preserve">Annual RevenuAnnuate</t>
   </si>
   <si>
     <t xml:space="preserve">Annual Cost</t>
@@ -77,7 +77,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -99,6 +99,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -143,8 +151,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -169,45 +181,48 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="1" width="8.54"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -240,7 +255,7 @@
         <v>695000</v>
       </c>
       <c r="K2" s="1" t="n">
-        <f aca="false">C2+E2+G2+I2</f>
+        <f aca="false">SUM(C2,E2,G2,I2)</f>
         <v>515000</v>
       </c>
     </row>
@@ -276,10 +291,6 @@
         <f aca="false">SUM(B3,D3,F3,H3)</f>
         <v>375000</v>
       </c>
-      <c r="K3" s="1" t="n">
-        <f aca="false">SUM(C3,E3,G3,I3)</f>
-        <v>270000</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
@@ -314,7 +325,7 @@
         <v>950000</v>
       </c>
       <c r="K4" s="1" t="n">
-        <f aca="false">SUM(C4,E4,G4,I4)</f>
+        <f aca="false">C4+E4+G4+I4</f>
         <v>460000</v>
       </c>
     </row>
@@ -351,7 +362,7 @@
         <v>135000</v>
       </c>
       <c r="K5" s="1" t="n">
-        <f aca="false">SUM(C5,E5,G5,I5)</f>
+        <f aca="false">C5+E5+G5+I5</f>
         <v>109000</v>
       </c>
     </row>
@@ -388,8 +399,14 @@
         <v>460000</v>
       </c>
       <c r="K6" s="1" t="n">
-        <f aca="false">SUM(C6,E6,G6,I6)</f>
-        <v>370000</v>
+        <f aca="false">C2+E2+G2+I2</f>
+        <v>515000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K7" s="1" t="n">
+        <f aca="false">C3+E3+G3+I3</f>
+        <v>270000</v>
       </c>
     </row>
   </sheetData>
